--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_55_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_55_IN_Piura.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C10" s="31">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>55.53</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C11" s="28">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>42.71</v>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>1.76</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C13" s="28">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>0.8592</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>0.8441</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>98.24</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>0.0151</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>1.76</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2104,11 +2104,11 @@
       </c>
       <c r="B26" s="20">
         <f>SUM(B25:B25)</f>
-        <v/>
+        <v>0.8595</v>
       </c>
       <c r="C26" s="21">
         <f>SUM(C25:C25)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D26" s="17" t="inlineStr"/>
       <c r="E26" s="17" t="inlineStr"/>
@@ -2227,6 +2227,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2621,6 +2622,7 @@
       <c r="F21" s="17" t="inlineStr"/>
       <c r="G21" s="17" t="inlineStr"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
@@ -2667,6 +2669,7 @@
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26" ht="120" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
@@ -3092,11 +3095,11 @@
       </c>
       <c r="B18" s="33">
         <f>SUM(B10:B17)</f>
-        <v/>
+        <v>484.3</v>
       </c>
       <c r="C18" s="21">
         <f>SUM(C10:C17)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -3106,19 +3109,19 @@
       <c r="E18" s="17" t="inlineStr"/>
       <c r="F18" s="17">
         <f>ROUND(AVERAGE(F10:F17),2)</f>
-        <v/>
+        <v>25.51</v>
       </c>
       <c r="G18" s="20">
         <f>ROUND(AVERAGE(G10:G17),4)</f>
-        <v/>
+        <v>0.6021</v>
       </c>
       <c r="H18" s="21">
         <f>ROUND(AVERAGE(H10:H17),2)</f>
-        <v/>
+        <v>66.1</v>
       </c>
       <c r="I18" s="21">
         <f>ROUND(AVERAGE(I10:I17),2)</f>
-        <v/>
+        <v>32.65</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
